--- a/docs/reports/內在價值報告_20261013.xlsx
+++ b/docs/reports/內在價值報告_20261013.xlsx
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>431.57</v>
+        <v>441.82</v>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
@@ -1438,22 +1438,22 @@
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="4" t="n">
-        <v>6265.31</v>
+        <v>6308.2253</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>539.2962</v>
+        <v>564.4848</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>5285.4917</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-93.09999999999999</v>
+        <v>-93</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4698.9825</v>
+        <v>4731.169</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>6</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>503.515</v>
+        <v>521.963</v>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AE14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>269.136</v>
+        <v>249.5</v>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr">
@@ -3494,22 +3494,22 @@
       </c>
       <c r="H24" s="8" t="inlineStr"/>
       <c r="I24" s="9" t="n">
-        <v>480.8055</v>
+        <v>480.8226</v>
       </c>
       <c r="J24" s="9" t="n">
         <v>9.3416</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>17.7683</v>
+        <v>17.7724</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>-44</v>
+        <v>-48.1</v>
       </c>
       <c r="M24" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>360.6041</v>
+        <v>360.6169</v>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AE24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>373.955</v>
+        <v>378.04</v>
       </c>
       <c r="E34" s="13" t="inlineStr"/>
       <c r="F34" s="12" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="H34" s="13" t="inlineStr"/>
       <c r="I34" s="14" t="n">
-        <v>369.4252</v>
+        <v>369.4244</v>
       </c>
       <c r="J34" s="14" t="n">
         <v>64.4277</v>
@@ -4711,13 +4711,13 @@
         <v>314.2098</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="M34" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>277.0689</v>
+        <v>277.0683</v>
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="AE34" s="12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF34" s="13" t="inlineStr">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="D48" s="24" t="n">
-        <v>343.045</v>
+        <v>345.79</v>
       </c>
       <c r="E48" s="23" t="inlineStr"/>
       <c r="F48" s="22" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="H48" s="23" t="inlineStr"/>
       <c r="I48" s="24" t="n">
-        <v>49.1602</v>
+        <v>49.1601</v>
       </c>
       <c r="J48" s="24" t="n">
         <v>9.446</v>
@@ -6405,13 +6405,13 @@
         <v>34.7808</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>597.8</v>
+        <v>603.4</v>
       </c>
       <c r="M48" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N48" s="24" t="n">
-        <v>36.8702</v>
+        <v>36.8701</v>
       </c>
       <c r="O48" s="22" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AE48" s="22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF48" s="23" t="inlineStr">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="D49" s="24" t="n">
-        <v>219.54</v>
+        <v>224.73</v>
       </c>
       <c r="E49" s="23" t="inlineStr"/>
       <c r="F49" s="22" t="inlineStr">
@@ -6518,16 +6518,16 @@
       </c>
       <c r="H49" s="23" t="inlineStr"/>
       <c r="I49" s="24" t="n">
-        <v>45.7474</v>
+        <v>45.7473</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>6.8363</v>
+        <v>6.8361</v>
       </c>
       <c r="K49" s="24" t="n">
         <v>31.5866</v>
       </c>
       <c r="L49" s="25" t="n">
-        <v>379.9</v>
+        <v>391.2</v>
       </c>
       <c r="M49" s="25" t="n">
         <v>25</v>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AE49" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF49" s="23" t="inlineStr">
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="D51" s="24" t="n">
-        <v>253.56</v>
+        <v>260.5</v>
       </c>
       <c r="E51" s="23" t="inlineStr"/>
       <c r="F51" s="22" t="inlineStr">
@@ -6767,7 +6767,7 @@
         <v>487.2973</v>
       </c>
       <c r="L51" s="25" t="n">
-        <v>136.8</v>
+        <v>143.3</v>
       </c>
       <c r="M51" s="25" t="n">
         <v>25</v>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="AE51" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF51" s="23" t="inlineStr">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="D52" s="24" t="n">
-        <v>358.794</v>
+        <v>355.5</v>
       </c>
       <c r="E52" s="23" t="inlineStr"/>
       <c r="F52" s="22" t="inlineStr">
@@ -6883,13 +6883,13 @@
         <v>62.856</v>
       </c>
       <c r="J52" s="24" t="n">
-        <v>2.017</v>
+        <v>2.0171</v>
       </c>
       <c r="K52" s="24" t="n">
         <v>15.3128</v>
       </c>
       <c r="L52" s="25" t="n">
-        <v>470.8</v>
+        <v>465.6</v>
       </c>
       <c r="M52" s="25" t="n">
         <v>25</v>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AE52" s="22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF52" s="23" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="D53" s="24" t="n">
-        <v>1146.22</v>
+        <v>1174.33</v>
       </c>
       <c r="E53" s="23" t="inlineStr"/>
       <c r="F53" s="22" t="inlineStr">
@@ -7002,22 +7002,22 @@
       </c>
       <c r="H53" s="23" t="inlineStr"/>
       <c r="I53" s="24" t="n">
-        <v>544.7381</v>
+        <v>544.725</v>
       </c>
       <c r="J53" s="24" t="n">
-        <v>58.8487</v>
+        <v>58.8462</v>
       </c>
       <c r="K53" s="24" t="n">
         <v>202.834</v>
       </c>
       <c r="L53" s="25" t="n">
-        <v>110.4</v>
+        <v>115.6</v>
       </c>
       <c r="M53" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N53" s="24" t="n">
-        <v>408.5536</v>
+        <v>408.5437</v>
       </c>
       <c r="O53" s="22" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="AE53" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF53" s="23" t="inlineStr">
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="D54" s="24" t="n">
-        <v>495.83</v>
+        <v>546.715</v>
       </c>
       <c r="E54" s="23" t="inlineStr"/>
       <c r="F54" s="22" t="inlineStr">
@@ -7124,22 +7124,22 @@
       </c>
       <c r="H54" s="23" t="inlineStr"/>
       <c r="I54" s="24" t="n">
-        <v>81.6729</v>
+        <v>81.6728</v>
       </c>
       <c r="J54" s="24" t="n">
-        <v>3.4477</v>
+        <v>3.4472</v>
       </c>
       <c r="K54" s="24" t="n">
         <v>86.59699999999999</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>507.1</v>
+        <v>569.4</v>
       </c>
       <c r="M54" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N54" s="24" t="n">
-        <v>61.2547</v>
+        <v>61.2546</v>
       </c>
       <c r="O54" s="22" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AE54" s="22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF54" s="23" t="inlineStr">
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="D55" s="24" t="n">
-        <v>369.03</v>
+        <v>393.515</v>
       </c>
       <c r="E55" s="23" t="inlineStr"/>
       <c r="F55" s="22" t="inlineStr">
@@ -7246,22 +7246,22 @@
       </c>
       <c r="H55" s="23" t="inlineStr"/>
       <c r="I55" s="24" t="n">
-        <v>54.2597</v>
+        <v>54.2594</v>
       </c>
       <c r="J55" s="24" t="n">
-        <v>9.348100000000001</v>
+        <v>9.348000000000001</v>
       </c>
       <c r="K55" s="24" t="n">
         <v>61.9902</v>
       </c>
       <c r="L55" s="25" t="n">
-        <v>580.1</v>
+        <v>625.2</v>
       </c>
       <c r="M55" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N55" s="24" t="n">
-        <v>40.6947</v>
+        <v>40.6946</v>
       </c>
       <c r="O55" s="22" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="AE55" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF55" s="23" t="inlineStr">
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="D58" s="24" t="n">
-        <v>283.66</v>
+        <v>338.28</v>
       </c>
       <c r="E58" s="23" t="inlineStr"/>
       <c r="F58" s="22" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="H58" s="23" t="inlineStr"/>
       <c r="I58" s="24" t="n">
-        <v>26.9669</v>
+        <v>26.9668</v>
       </c>
       <c r="J58" s="24" t="n">
         <v>1.7995</v>
@@ -7621,13 +7621,13 @@
         <v>8.8208</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>951.9</v>
+        <v>1154.4</v>
       </c>
       <c r="M58" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N58" s="24" t="n">
-        <v>20.2252</v>
+        <v>20.2251</v>
       </c>
       <c r="O58" s="22" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="AE58" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF58" s="23" t="inlineStr">
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="D59" s="24" t="n">
-        <v>167.445</v>
+        <v>191.55</v>
       </c>
       <c r="E59" s="23" t="inlineStr"/>
       <c r="F59" s="22" t="inlineStr">
@@ -7734,22 +7734,22 @@
       </c>
       <c r="H59" s="23" t="inlineStr"/>
       <c r="I59" s="24" t="n">
-        <v>21.4774</v>
+        <v>21.4772</v>
       </c>
       <c r="J59" s="24" t="n">
         <v>4.7985</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>5.0403</v>
+        <v>5.04</v>
       </c>
       <c r="L59" s="25" t="n">
-        <v>679.6</v>
+        <v>791.9</v>
       </c>
       <c r="M59" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N59" s="24" t="n">
-        <v>16.108</v>
+        <v>16.1079</v>
       </c>
       <c r="O59" s="22" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AE59" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF59" s="23" t="inlineStr">
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="D60" s="24" t="n">
-        <v>146.33</v>
+        <v>152.815</v>
       </c>
       <c r="E60" s="23" t="inlineStr"/>
       <c r="F60" s="22" t="inlineStr">
@@ -7863,7 +7863,7 @@
         <v>13.4653</v>
       </c>
       <c r="L60" s="25" t="n">
-        <v>623.6</v>
+        <v>655.7</v>
       </c>
       <c r="M60" s="25" t="n">
         <v>25</v>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="AE60" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF60" s="23" t="inlineStr">
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="D61" s="24" t="n">
-        <v>32.975</v>
+        <v>32.115</v>
       </c>
       <c r="E61" s="23" t="inlineStr"/>
       <c r="F61" s="22" t="inlineStr">
@@ -7985,7 +7985,7 @@
         <v>5.2053</v>
       </c>
       <c r="L61" s="25" t="n">
-        <v>656</v>
+        <v>636.3</v>
       </c>
       <c r="M61" s="25" t="n">
         <v>25</v>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="AE61" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF61" s="23" t="inlineStr">
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="D62" s="24" t="n">
-        <v>107.11</v>
+        <v>113.75</v>
       </c>
       <c r="E62" s="23" t="inlineStr"/>
       <c r="F62" s="22" t="inlineStr">
@@ -8098,22 +8098,22 @@
       </c>
       <c r="H62" s="23" t="inlineStr"/>
       <c r="I62" s="24" t="n">
-        <v>11.8315</v>
+        <v>8.831300000000001</v>
       </c>
       <c r="J62" s="24" t="n">
-        <v>0.1989</v>
+        <v>0.1988</v>
       </c>
       <c r="K62" s="24" t="n">
-        <v>28.2934</v>
+        <v>9.5785</v>
       </c>
       <c r="L62" s="25" t="n">
-        <v>805.3</v>
+        <v>1188</v>
       </c>
       <c r="M62" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N62" s="24" t="n">
-        <v>8.873699999999999</v>
+        <v>6.6234</v>
       </c>
       <c r="O62" s="22" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>1.5</v>
       </c>
       <c r="W62" s="22" t="n">
-        <v>66.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="X62" s="23" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AE62" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF62" s="23" t="inlineStr">
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="D64" s="24" t="n">
-        <v>87.78</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="E64" s="23" t="inlineStr"/>
       <c r="F64" s="22" t="inlineStr">
@@ -8351,7 +8351,7 @@
         <v>11.4611</v>
       </c>
       <c r="L64" s="25" t="n">
-        <v>524.8</v>
+        <v>542.1</v>
       </c>
       <c r="M64" s="25" t="n">
         <v>25</v>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="AE64" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF64" s="23" t="inlineStr">
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="D66" s="24" t="n">
-        <v>365.1</v>
+        <v>376</v>
       </c>
       <c r="E66" s="23" t="inlineStr"/>
       <c r="F66" s="22" t="inlineStr">
@@ -8595,7 +8595,7 @@
         <v>4.6574</v>
       </c>
       <c r="L66" s="25" t="n">
-        <v>7961.7</v>
+        <v>8202.4</v>
       </c>
       <c r="M66" s="25" t="n">
         <v>25</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="AE66" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF66" s="23" t="inlineStr">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="D68" s="29" t="n">
-        <v>147.92</v>
+        <v>153.786</v>
       </c>
       <c r="E68" s="28" t="inlineStr"/>
       <c r="F68" s="27" t="inlineStr">
@@ -8828,28 +8828,24 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H68" s="28" t="inlineStr">
-        <is>
-          <t>比特幣財庫</t>
-        </is>
-      </c>
+      <c r="H68" s="28" t="inlineStr"/>
       <c r="I68" s="29" t="n">
-        <v>21296.5965</v>
+        <v>19409.9873</v>
       </c>
       <c r="J68" s="29" t="n">
-        <v>21296.5965</v>
+        <v>19409.9873</v>
       </c>
       <c r="K68" s="29" t="n">
-        <v>21296.5965</v>
+        <v>19409.9873</v>
       </c>
       <c r="L68" s="30" t="n">
-        <v>-99.3</v>
+        <v>-99.2</v>
       </c>
       <c r="M68" s="30" t="n">
         <v>25</v>
       </c>
       <c r="N68" s="29" t="n">
-        <v>15972.4474</v>
+        <v>14557.4905</v>
       </c>
       <c r="O68" s="27" t="inlineStr">
         <is>
@@ -8915,7 +8911,7 @@
       </c>
       <c r="AE68" s="27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF68" s="28" t="inlineStr">
@@ -12234,10 +12230,10 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>343.045</v>
+        <v>345.79</v>
       </c>
       <c r="D52" s="34" t="n">
-        <v>49.1602</v>
+        <v>49.1601</v>
       </c>
       <c r="E52" s="34" t="n">
         <v>9.446</v>
@@ -12248,10 +12244,10 @@
       <c r="G52" s="34" t="inlineStr"/>
       <c r="H52" s="34" t="inlineStr"/>
       <c r="I52" s="34" t="n">
-        <v>8.8986</v>
+        <v>8.898300000000001</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>12.4164</v>
+        <v>12.4163</v>
       </c>
       <c r="K52" s="34" t="n">
         <v>494.7644</v>
@@ -12289,7 +12285,7 @@
         </is>
       </c>
       <c r="C53" s="34" t="n">
-        <v>253.56</v>
+        <v>260.5</v>
       </c>
       <c r="D53" s="34" t="n">
         <v>107.0856</v>
@@ -12340,7 +12336,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>503.515</v>
+        <v>521.963</v>
       </c>
       <c r="D54" s="34" t="n">
         <v>1600617.8442</v>
@@ -12360,7 +12356,7 @@
       </c>
       <c r="L54" s="34" t="inlineStr"/>
       <c r="M54" s="34" t="n">
-        <v>7.31</v>
+        <v>7.35</v>
       </c>
       <c r="N54" s="34" t="n">
         <v>8.800000000000001</v>
@@ -12391,10 +12387,10 @@
         </is>
       </c>
       <c r="C55" s="34" t="n">
-        <v>283.66</v>
+        <v>338.28</v>
       </c>
       <c r="D55" s="34" t="n">
-        <v>26.9669</v>
+        <v>26.9668</v>
       </c>
       <c r="E55" s="34" t="n">
         <v>7.0983</v>
@@ -12405,7 +12401,7 @@
       <c r="G55" s="34" t="inlineStr"/>
       <c r="H55" s="34" t="inlineStr"/>
       <c r="I55" s="34" t="n">
-        <v>0.7776</v>
+        <v>0.7772</v>
       </c>
       <c r="J55" s="34" t="n">
         <v>1.7995</v>
@@ -12430,7 +12426,7 @@
       </c>
       <c r="Q55" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 1.25, "BVPS": 1.7915}, "graham_formula": {"g(上限10%)": -0.0991, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -0.7283, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.3149, "常態NOPAT": 418630512.0, "WACC": 0.0878, "淨現金": -1788624000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.04, "目標營業利益率": 0.3149, "WACC": 0.0878, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.698}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 1.25, "BVPS": 1.7915}, "graham_formula": {"g(上限10%)": -0.0991, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -0.7283, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.3149, "常態NOPAT": 418630512.0, "WACC": 0.0879, "淨現金": -1788624000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.04, "目標營業利益率": 0.3149, "WACC": 0.0879, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.698}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -12446,10 +12442,10 @@
         </is>
       </c>
       <c r="C56" s="34" t="n">
-        <v>167.445</v>
+        <v>191.55</v>
       </c>
       <c r="D56" s="34" t="n">
-        <v>21.4774</v>
+        <v>21.4772</v>
       </c>
       <c r="E56" s="34" t="n">
         <v>3.6112</v>
@@ -12460,7 +12456,7 @@
       <c r="G56" s="34" t="inlineStr"/>
       <c r="H56" s="34" t="inlineStr"/>
       <c r="I56" s="34" t="n">
-        <v>5.0403</v>
+        <v>5.04</v>
       </c>
       <c r="J56" s="34" t="inlineStr"/>
       <c r="K56" s="34" t="n">
@@ -12499,7 +12495,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>358.794</v>
+        <v>355.5</v>
       </c>
       <c r="D57" s="34" t="n">
         <v>62.856</v>
@@ -12515,7 +12511,7 @@
       </c>
       <c r="H57" s="34" t="inlineStr"/>
       <c r="I57" s="34" t="n">
-        <v>2.017</v>
+        <v>2.0171</v>
       </c>
       <c r="J57" s="34" t="n">
         <v>3.797</v>
@@ -12556,10 +12552,10 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>269.136</v>
+        <v>249.5</v>
       </c>
       <c r="D58" s="34" t="n">
-        <v>480.8055</v>
+        <v>480.8226</v>
       </c>
       <c r="E58" s="34" t="n">
         <v>9.3416</v>
@@ -12570,17 +12566,17 @@
       <c r="G58" s="34" t="inlineStr"/>
       <c r="H58" s="34" t="inlineStr"/>
       <c r="I58" s="34" t="n">
-        <v>15.4517</v>
+        <v>15.5059</v>
       </c>
       <c r="J58" s="34" t="n">
-        <v>17.7683</v>
+        <v>17.7724</v>
       </c>
       <c r="K58" s="34" t="n">
         <v>6466.5299</v>
       </c>
       <c r="L58" s="34" t="inlineStr"/>
       <c r="M58" s="34" t="n">
-        <v>8.52</v>
+        <v>8.5</v>
       </c>
       <c r="N58" s="34" t="n">
         <v>8.800000000000001</v>
@@ -12595,7 +12591,7 @@
       </c>
       <c r="Q58" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.11, "BVPS": 35.2592}, "graham_formula": {"g(上限10%)": 0.0344, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -30.6285, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.1926, "常態NOPAT": 4616104077.0, "WACC": 0.0852, "淨現金": -16922000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": -0.0032, "永續g": 0.04, "目標營業利益率": 0.1926, "WACC": 0.0852, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.544}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.11, "BVPS": 35.2592}, "graham_formula": {"g(上限10%)": 0.0344, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -30.6285, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.1926, "常態NOPAT": 4616104077.0, "WACC": 0.085, "淨現金": -16922000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": -0.0032, "永續g": 0.04, "目標營業利益率": 0.1926, "WACC": 0.085, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.544}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12607,7 @@
         </is>
       </c>
       <c r="C59" s="34" t="n">
-        <v>87.78</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="D59" s="34" t="n">
         <v>14.0496</v>
@@ -12648,7 +12644,7 @@
       </c>
       <c r="Q59" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.51, "BVPS": 0.5956}, "graham_formula": {"g(上限10%)": 0.0928, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -0.8395, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.2049, "常態NOPAT": 2031954765.0, "WACC": 0.0876, "淨現金": -23472000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.053, "永續g": 0.04, "目標營業利益率": 0.2049, "WACC": 0.0876, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.637}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.51, "BVPS": 0.5956}, "graham_formula": {"g(上限10%)": 0.0928, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -0.8395, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.2049, "常態NOPAT": 2031954765.0, "WACC": 0.0877, "淨現金": -23472000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.053, "永續g": 0.04, "目標營業利益率": 0.2049, "WACC": 0.0877, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.637}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -12664,10 +12660,10 @@
         </is>
       </c>
       <c r="C60" s="34" t="n">
-        <v>1146.22</v>
+        <v>1174.33</v>
       </c>
       <c r="D60" s="34" t="n">
-        <v>544.7381</v>
+        <v>544.725</v>
       </c>
       <c r="E60" s="34" t="n">
         <v>83.318</v>
@@ -12678,17 +12674,17 @@
       <c r="G60" s="34" t="inlineStr"/>
       <c r="H60" s="34" t="inlineStr"/>
       <c r="I60" s="34" t="n">
-        <v>15.5319</v>
+        <v>15.4897</v>
       </c>
       <c r="J60" s="34" t="n">
-        <v>58.8487</v>
+        <v>58.8462</v>
       </c>
       <c r="K60" s="34" t="n">
         <v>6600.4801</v>
       </c>
       <c r="L60" s="34" t="inlineStr"/>
       <c r="M60" s="34" t="n">
-        <v>8.550000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="N60" s="34" t="n">
         <v>8.800000000000001</v>
@@ -12703,7 +12699,7 @@
       </c>
       <c r="Q60" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 8.5727, "BVPS": 35.9895}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -80.7295, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.2553, "常態NOPAT": 5181832855.0, "WACC": 0.0855, "淨現金": -45958000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.04, "目標營業利益率": 0.2553, "WACC": 0.0855, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.74}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 8.5727, "BVPS": 35.9895}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -80.7295, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.2553, "常態NOPAT": 5181832855.0, "WACC": 0.0856, "淨現金": -45958000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.04, "目標營業利益率": 0.2553, "WACC": 0.0856, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.74}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -12719,10 +12715,10 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>495.83</v>
+        <v>546.715</v>
       </c>
       <c r="D61" s="34" t="n">
-        <v>81.6729</v>
+        <v>81.6728</v>
       </c>
       <c r="E61" s="34" t="n">
         <v>19.923</v>
@@ -12733,7 +12729,7 @@
       <c r="G61" s="34" t="inlineStr"/>
       <c r="H61" s="34" t="inlineStr"/>
       <c r="I61" s="34" t="n">
-        <v>3.4477</v>
+        <v>3.4472</v>
       </c>
       <c r="J61" s="34" t="n">
         <v>3.3891</v>
@@ -12774,10 +12770,10 @@
         </is>
       </c>
       <c r="C62" s="34" t="n">
-        <v>147.92</v>
+        <v>153.786</v>
       </c>
       <c r="D62" s="34" t="n">
-        <v>21296.5965</v>
+        <v>19409.9873</v>
       </c>
       <c r="E62" s="34" t="inlineStr"/>
       <c r="F62" s="34" t="inlineStr"/>
@@ -12786,11 +12782,11 @@
       <c r="I62" s="34" t="inlineStr"/>
       <c r="J62" s="34" t="inlineStr"/>
       <c r="K62" s="34" t="n">
-        <v>21296.5965</v>
+        <v>19409.9873</v>
       </c>
       <c r="L62" s="34" t="inlineStr"/>
       <c r="M62" s="34" t="n">
-        <v>9.470000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="N62" s="34" t="n">
         <v>10.15</v>
@@ -12805,7 +12801,7 @@
       </c>
       <c r="Q62" s="33" t="inlineStr">
         <is>
-          <t>{"ncav": {"NCAV/股": 0.0, "NNWC/股": -12.2071, "net-net買點": 0.0}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.1015, "留存成長g": 0.0965, "合理PB": 180.7}}</t>
+          <t>{"ncav": {"NCAV/股": 0.0, "NNWC/股": -11.1257, "net-net買點": 0.0}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.1015, "留存成長g": 0.0965, "合理PB": 180.7}}</t>
         </is>
       </c>
     </row>
@@ -12821,10 +12817,10 @@
         </is>
       </c>
       <c r="C63" s="34" t="n">
-        <v>219.54</v>
+        <v>224.73</v>
       </c>
       <c r="D63" s="34" t="n">
-        <v>45.7474</v>
+        <v>45.7473</v>
       </c>
       <c r="E63" s="34" t="n">
         <v>8.797599999999999</v>
@@ -12837,10 +12833,10 @@
       </c>
       <c r="H63" s="34" t="inlineStr"/>
       <c r="I63" s="34" t="n">
-        <v>6.8363</v>
+        <v>6.8361</v>
       </c>
       <c r="J63" s="34" t="n">
-        <v>15.1803</v>
+        <v>15.1802</v>
       </c>
       <c r="K63" s="34" t="n">
         <v>467.9343</v>
@@ -12878,7 +12874,7 @@
         </is>
       </c>
       <c r="C64" s="34" t="n">
-        <v>146.33</v>
+        <v>152.815</v>
       </c>
       <c r="D64" s="34" t="n">
         <v>20.2227</v>
@@ -12892,7 +12888,7 @@
       <c r="G64" s="34" t="inlineStr"/>
       <c r="H64" s="34" t="inlineStr"/>
       <c r="I64" s="34" t="n">
-        <v>0.5163</v>
+        <v>0.5162</v>
       </c>
       <c r="J64" s="34" t="n">
         <v>0.6433</v>
@@ -12933,7 +12929,7 @@
         </is>
       </c>
       <c r="C65" s="34" t="n">
-        <v>32.975</v>
+        <v>32.115</v>
       </c>
       <c r="D65" s="34" t="n">
         <v>4.3617</v>
@@ -12947,7 +12943,7 @@
       <c r="G65" s="34" t="inlineStr"/>
       <c r="H65" s="34" t="inlineStr"/>
       <c r="I65" s="34" t="n">
-        <v>0.1443</v>
+        <v>0.1444</v>
       </c>
       <c r="J65" s="34" t="n">
         <v>0.2487</v>
@@ -12988,7 +12984,7 @@
         </is>
       </c>
       <c r="C66" s="34" t="n">
-        <v>365.1</v>
+        <v>376</v>
       </c>
       <c r="D66" s="34" t="n">
         <v>4.5288</v>
@@ -13045,10 +13041,10 @@
         </is>
       </c>
       <c r="C67" s="34" t="n">
-        <v>431.57</v>
+        <v>441.82</v>
       </c>
       <c r="D67" s="34" t="n">
-        <v>6265.31</v>
+        <v>6308.2253</v>
       </c>
       <c r="E67" s="34" t="n">
         <v>1397.4929</v>
@@ -13061,23 +13057,23 @@
       </c>
       <c r="H67" s="34" t="inlineStr"/>
       <c r="I67" s="34" t="n">
-        <v>539.2962</v>
+        <v>564.4848</v>
       </c>
       <c r="J67" s="34" t="n">
-        <v>905.7868999999999</v>
+        <v>908.5782</v>
       </c>
       <c r="K67" s="34" t="n">
-        <v>70736.5186</v>
+        <v>71261.0684</v>
       </c>
       <c r="L67" s="34" t="inlineStr"/>
       <c r="M67" s="34" t="n">
-        <v>9.44</v>
+        <v>8.77</v>
       </c>
       <c r="N67" s="34" t="n">
-        <v>9.470000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O67" s="32" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="P67" s="33" t="inlineStr">
         <is>
@@ -13086,7 +13082,7 @@
       </c>
       <c r="Q67" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 223.39, "BVPS": 388.5554}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.053}, "ncav": {"NCAV/股": 100.5449, "NNWC/股": 48.9033, "net-net買點": 67.0635}, "epv": {"常態營業利益率": 0.4902, "常態NOPAT": 515111631753.0, "WACC": 0.0944, "淨現金": 3468786165000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.04, "目標營業利益率": 0.4902, "WACC": 0.0944, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.644}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.0948, "留存成長g": 0.0897, "合理PB": 182.05}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 223.39, "BVPS": 388.5554}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.053}, "ncav": {"NCAV/股": 100.5449, "NNWC/股": 48.9033, "net-net買點": 67.0635}, "epv": {"常態營業利益率": 0.4902, "常態NOPAT": 515111631753.0, "WACC": 0.0877, "淨現金": 3468786165000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.04, "目標營業利益率": 0.4902, "WACC": 0.0877, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.642}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -13102,10 +13098,10 @@
         </is>
       </c>
       <c r="C68" s="34" t="n">
-        <v>373.955</v>
+        <v>378.04</v>
       </c>
       <c r="D68" s="34" t="n">
-        <v>369.4252</v>
+        <v>369.4244</v>
       </c>
       <c r="E68" s="34" t="n">
         <v>64.4277</v>
@@ -13116,7 +13112,7 @@
       <c r="G68" s="34" t="inlineStr"/>
       <c r="H68" s="34" t="inlineStr"/>
       <c r="I68" s="34" t="n">
-        <v>4.9397</v>
+        <v>4.9379</v>
       </c>
       <c r="J68" s="34" t="inlineStr"/>
       <c r="K68" s="34" t="n">
@@ -13124,7 +13120,7 @@
       </c>
       <c r="L68" s="34" t="inlineStr"/>
       <c r="M68" s="34" t="n">
-        <v>8.66</v>
+        <v>8.67</v>
       </c>
       <c r="N68" s="34" t="n">
         <v>8.800000000000001</v>
@@ -13155,10 +13151,10 @@
         </is>
       </c>
       <c r="C69" s="34" t="n">
-        <v>369.03</v>
+        <v>393.515</v>
       </c>
       <c r="D69" s="34" t="n">
-        <v>54.2597</v>
+        <v>54.2594</v>
       </c>
       <c r="E69" s="34" t="n">
         <v>12.8744</v>
@@ -13169,10 +13165,10 @@
       <c r="G69" s="34" t="inlineStr"/>
       <c r="H69" s="34" t="inlineStr"/>
       <c r="I69" s="34" t="n">
-        <v>4.9095</v>
+        <v>4.9086</v>
       </c>
       <c r="J69" s="34" t="n">
-        <v>9.348100000000001</v>
+        <v>9.348000000000001</v>
       </c>
       <c r="K69" s="34" t="n">
         <v>515.6686999999999</v>
@@ -13210,21 +13206,21 @@
         </is>
       </c>
       <c r="C70" s="34" t="n">
-        <v>107.11</v>
+        <v>113.75</v>
       </c>
       <c r="D70" s="34" t="n">
-        <v>11.8315</v>
+        <v>8.831300000000001</v>
       </c>
       <c r="E70" s="34" t="n">
-        <v>4.7517</v>
+        <v>2.7648</v>
       </c>
       <c r="F70" s="34" t="n">
-        <v>28.2934</v>
+        <v>9.5785</v>
       </c>
       <c r="G70" s="34" t="inlineStr"/>
       <c r="H70" s="34" t="inlineStr"/>
       <c r="I70" s="34" t="n">
-        <v>0.1989</v>
+        <v>0.1988</v>
       </c>
       <c r="J70" s="34" t="n">
         <v>0.111</v>
@@ -13249,7 +13245,7 @@
       </c>
       <c r="Q70" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 1.92, "BVPS": 0.5227}, "graham_formula": {"g(上限10%)": 0.0463, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -0.7368, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.0418, "常態NOPAT": 6397063411.0, "WACC": 0.0879, "淨現金": -35412000000.0}, "damodaran_fcff": {"銷售/資本": 1.505, "g1": 0.0514, "永續g": 0.04, "目標營業利益率": 0.0418, "WACC": 0.0879, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.934}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.65, "BVPS": 0.5227}, "graham_formula": {"g(上限10%)": 0.0463, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -0.7368, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.0418, "常態NOPAT": 6397063411.0, "WACC": 0.0879, "淨現金": -35412000000.0}, "damodaran_fcff": {"銷售/資本": 1.505, "g1": 0.0514, "永續g": 0.04, "目標營業利益率": 0.0418, "WACC": 0.0879, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.934}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -15642,7 +15638,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>343.045</v>
+        <v>345.79</v>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
@@ -15653,16 +15649,16 @@
         <v>24.5801</v>
       </c>
       <c r="F52" s="24" t="n">
-        <v>36.8702</v>
+        <v>36.8701</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>56.5342</v>
+        <v>56.5341</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>73.7403</v>
+        <v>73.7402</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>73.7403</v>
+        <v>73.7402</v>
       </c>
       <c r="J52" s="26" t="inlineStr">
         <is>
@@ -15670,10 +15666,10 @@
         </is>
       </c>
       <c r="K52" s="24" t="n">
-        <v>6.9781</v>
+        <v>7.034</v>
       </c>
       <c r="L52" s="24" t="n">
-        <v>36.8702</v>
+        <v>36.8701</v>
       </c>
     </row>
     <row r="53">
@@ -15688,7 +15684,7 @@
         </is>
       </c>
       <c r="C53" s="24" t="n">
-        <v>253.56</v>
+        <v>260.5</v>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
@@ -15716,7 +15712,7 @@
         </is>
       </c>
       <c r="K53" s="24" t="n">
-        <v>2.3678</v>
+        <v>2.4326</v>
       </c>
       <c r="L53" s="24" t="n">
         <v>80.3142</v>
@@ -15734,7 +15730,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>503.515</v>
+        <v>521.963</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
@@ -15780,7 +15776,7 @@
         </is>
       </c>
       <c r="C55" s="24" t="n">
-        <v>283.66</v>
+        <v>338.28</v>
       </c>
       <c r="D55" s="22" t="inlineStr">
         <is>
@@ -15788,19 +15784,19 @@
         </is>
       </c>
       <c r="E55" s="24" t="n">
-        <v>13.4835</v>
+        <v>13.4834</v>
       </c>
       <c r="F55" s="24" t="n">
-        <v>20.2252</v>
+        <v>20.2251</v>
       </c>
       <c r="G55" s="24" t="n">
-        <v>31.012</v>
+        <v>31.0118</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>40.4504</v>
+        <v>40.4502</v>
       </c>
       <c r="I55" s="24" t="n">
-        <v>40.4504</v>
+        <v>40.4502</v>
       </c>
       <c r="J55" s="26" t="inlineStr">
         <is>
@@ -15808,10 +15804,10 @@
         </is>
       </c>
       <c r="K55" s="24" t="n">
-        <v>10.5188</v>
+        <v>12.5443</v>
       </c>
       <c r="L55" s="24" t="n">
-        <v>20.2252</v>
+        <v>20.2251</v>
       </c>
     </row>
     <row r="56">
@@ -15826,7 +15822,7 @@
         </is>
       </c>
       <c r="C56" s="24" t="n">
-        <v>167.445</v>
+        <v>191.55</v>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
@@ -15834,19 +15830,19 @@
         </is>
       </c>
       <c r="E56" s="24" t="n">
-        <v>10.7387</v>
+        <v>10.7386</v>
       </c>
       <c r="F56" s="24" t="n">
-        <v>16.108</v>
+        <v>16.1079</v>
       </c>
       <c r="G56" s="24" t="n">
-        <v>24.699</v>
+        <v>24.6988</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>32.2161</v>
+        <v>32.2158</v>
       </c>
       <c r="I56" s="24" t="n">
-        <v>32.2161</v>
+        <v>32.2158</v>
       </c>
       <c r="J56" s="26" t="inlineStr">
         <is>
@@ -15854,10 +15850,10 @@
         </is>
       </c>
       <c r="K56" s="24" t="n">
-        <v>7.7963</v>
+        <v>8.918799999999999</v>
       </c>
       <c r="L56" s="24" t="n">
-        <v>16.108</v>
+        <v>16.1079</v>
       </c>
     </row>
     <row r="57">
@@ -15872,7 +15868,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>358.794</v>
+        <v>355.5</v>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
@@ -15900,7 +15896,7 @@
         </is>
       </c>
       <c r="K57" s="24" t="n">
-        <v>5.7082</v>
+        <v>5.6558</v>
       </c>
       <c r="L57" s="24" t="n">
         <v>47.142</v>
@@ -15918,7 +15914,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>269.136</v>
+        <v>249.5</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -15926,19 +15922,19 @@
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>240.4027</v>
+        <v>240.4113</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>360.6041</v>
+        <v>360.6169</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>552.9263</v>
+        <v>552.946</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>721.2082</v>
+        <v>721.2338999999999</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>721.2082</v>
+        <v>721.2338999999999</v>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
@@ -15946,10 +15942,10 @@
         </is>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.5598</v>
+        <v>0.5189</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>360.6041</v>
+        <v>360.6169</v>
       </c>
     </row>
     <row r="59">
@@ -15964,7 +15960,7 @@
         </is>
       </c>
       <c r="C59" s="24" t="n">
-        <v>87.78</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
@@ -15992,7 +15988,7 @@
         </is>
       </c>
       <c r="K59" s="24" t="n">
-        <v>6.2479</v>
+        <v>6.4208</v>
       </c>
       <c r="L59" s="24" t="n">
         <v>10.5372</v>
@@ -16010,7 +16006,7 @@
         </is>
       </c>
       <c r="C60" s="24" t="n">
-        <v>1146.22</v>
+        <v>1174.33</v>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
@@ -16018,19 +16014,19 @@
         </is>
       </c>
       <c r="E60" s="24" t="n">
-        <v>272.3691</v>
+        <v>272.3625</v>
       </c>
       <c r="F60" s="24" t="n">
-        <v>408.5536</v>
+        <v>408.5437</v>
       </c>
       <c r="G60" s="24" t="n">
-        <v>626.4488</v>
+        <v>626.4337</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>817.1072</v>
+        <v>817.0875</v>
       </c>
       <c r="I60" s="24" t="n">
-        <v>817.1072</v>
+        <v>817.0875</v>
       </c>
       <c r="J60" s="26" t="inlineStr">
         <is>
@@ -16038,10 +16034,10 @@
         </is>
       </c>
       <c r="K60" s="24" t="n">
-        <v>2.1042</v>
+        <v>2.1558</v>
       </c>
       <c r="L60" s="24" t="n">
-        <v>408.5536</v>
+        <v>408.5437</v>
       </c>
     </row>
     <row r="61">
@@ -16056,7 +16052,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>495.83</v>
+        <v>546.715</v>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
@@ -16064,19 +16060,19 @@
         </is>
       </c>
       <c r="E61" s="24" t="n">
-        <v>40.8365</v>
+        <v>40.8364</v>
       </c>
       <c r="F61" s="24" t="n">
-        <v>61.2547</v>
+        <v>61.2546</v>
       </c>
       <c r="G61" s="24" t="n">
-        <v>93.9239</v>
+        <v>93.9237</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>122.5094</v>
+        <v>122.5092</v>
       </c>
       <c r="I61" s="24" t="n">
-        <v>122.5094</v>
+        <v>122.5092</v>
       </c>
       <c r="J61" s="26" t="inlineStr">
         <is>
@@ -16084,10 +16080,10 @@
         </is>
       </c>
       <c r="K61" s="24" t="n">
-        <v>6.0709</v>
+        <v>6.694</v>
       </c>
       <c r="L61" s="24" t="n">
-        <v>61.2547</v>
+        <v>61.2546</v>
       </c>
     </row>
     <row r="62">
@@ -16102,7 +16098,7 @@
         </is>
       </c>
       <c r="C62" s="29" t="n">
-        <v>147.92</v>
+        <v>153.786</v>
       </c>
       <c r="D62" s="27" t="inlineStr">
         <is>
@@ -16110,19 +16106,19 @@
         </is>
       </c>
       <c r="E62" s="29" t="n">
-        <v>10648.2983</v>
+        <v>9704.9936</v>
       </c>
       <c r="F62" s="29" t="n">
-        <v>15972.4474</v>
+        <v>14557.4905</v>
       </c>
       <c r="G62" s="29" t="n">
-        <v>24491.086</v>
+        <v>22321.4854</v>
       </c>
       <c r="H62" s="29" t="n">
-        <v>31944.8948</v>
+        <v>29114.9809</v>
       </c>
       <c r="I62" s="29" t="n">
-        <v>31944.8948</v>
+        <v>29114.9809</v>
       </c>
       <c r="J62" s="31" t="inlineStr">
         <is>
@@ -16130,10 +16126,10 @@
         </is>
       </c>
       <c r="K62" s="29" t="n">
-        <v>0.0069</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="L62" s="29" t="n">
-        <v>15972.4474</v>
+        <v>14557.4905</v>
       </c>
     </row>
     <row r="63">
@@ -16148,7 +16144,7 @@
         </is>
       </c>
       <c r="C63" s="24" t="n">
-        <v>219.54</v>
+        <v>224.73</v>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
@@ -16162,7 +16158,7 @@
         <v>34.3105</v>
       </c>
       <c r="G63" s="24" t="n">
-        <v>52.6095</v>
+        <v>52.6094</v>
       </c>
       <c r="H63" s="24" t="n">
         <v>68.621</v>
@@ -16176,7 +16172,7 @@
         </is>
       </c>
       <c r="K63" s="24" t="n">
-        <v>4.799</v>
+        <v>4.9124</v>
       </c>
       <c r="L63" s="24" t="n">
         <v>34.3105</v>
@@ -16194,7 +16190,7 @@
         </is>
       </c>
       <c r="C64" s="24" t="n">
-        <v>146.33</v>
+        <v>152.815</v>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
@@ -16202,7 +16198,7 @@
         </is>
       </c>
       <c r="E64" s="24" t="n">
-        <v>10.1114</v>
+        <v>10.1113</v>
       </c>
       <c r="F64" s="24" t="n">
         <v>15.167</v>
@@ -16211,10 +16207,10 @@
         <v>23.2561</v>
       </c>
       <c r="H64" s="24" t="n">
-        <v>30.3341</v>
+        <v>30.334</v>
       </c>
       <c r="I64" s="24" t="n">
-        <v>30.3341</v>
+        <v>30.334</v>
       </c>
       <c r="J64" s="26" t="inlineStr">
         <is>
@@ -16222,7 +16218,7 @@
         </is>
       </c>
       <c r="K64" s="24" t="n">
-        <v>7.2359</v>
+        <v>7.5566</v>
       </c>
       <c r="L64" s="24" t="n">
         <v>15.167</v>
@@ -16240,7 +16236,7 @@
         </is>
       </c>
       <c r="C65" s="24" t="n">
-        <v>32.975</v>
+        <v>32.115</v>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
@@ -16254,7 +16250,7 @@
         <v>3.2713</v>
       </c>
       <c r="G65" s="24" t="n">
-        <v>5.0159</v>
+        <v>5.016</v>
       </c>
       <c r="H65" s="24" t="n">
         <v>6.5425</v>
@@ -16268,7 +16264,7 @@
         </is>
       </c>
       <c r="K65" s="24" t="n">
-        <v>7.5601</v>
+        <v>7.363</v>
       </c>
       <c r="L65" s="24" t="n">
         <v>3.2713</v>
@@ -16286,7 +16282,7 @@
         </is>
       </c>
       <c r="C66" s="24" t="n">
-        <v>365.1</v>
+        <v>376</v>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
@@ -16314,7 +16310,7 @@
         </is>
       </c>
       <c r="K66" s="24" t="n">
-        <v>80.6177</v>
+        <v>83.0245</v>
       </c>
       <c r="L66" s="24" t="n">
         <v>3.3966</v>
@@ -16332,7 +16328,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>431.57</v>
+        <v>441.82</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
@@ -16340,19 +16336,19 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>3132.655</v>
+        <v>3154.1127</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>4698.9825</v>
+        <v>4731.169</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>7205.1065</v>
+        <v>7254.4591</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>9397.965099999999</v>
+        <v>9462.338</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>9397.965099999999</v>
+        <v>9462.338</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -16360,10 +16356,10 @@
         </is>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0.0689</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>4698.9825</v>
+        <v>4731.169</v>
       </c>
     </row>
     <row r="68">
@@ -16378,7 +16374,7 @@
         </is>
       </c>
       <c r="C68" s="14" t="n">
-        <v>373.955</v>
+        <v>378.04</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
@@ -16386,19 +16382,19 @@
         </is>
       </c>
       <c r="E68" s="14" t="n">
-        <v>184.7126</v>
+        <v>184.7122</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>277.0689</v>
+        <v>277.0683</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>424.839</v>
+        <v>424.8381</v>
       </c>
       <c r="H68" s="14" t="n">
-        <v>554.1378</v>
+        <v>554.1366</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>554.1378</v>
+        <v>554.1366</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -16406,10 +16402,10 @@
         </is>
       </c>
       <c r="K68" s="14" t="n">
-        <v>1.0123</v>
+        <v>1.0233</v>
       </c>
       <c r="L68" s="14" t="n">
-        <v>277.0689</v>
+        <v>277.0683</v>
       </c>
     </row>
     <row r="69">
@@ -16424,7 +16420,7 @@
         </is>
       </c>
       <c r="C69" s="24" t="n">
-        <v>369.03</v>
+        <v>393.515</v>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
@@ -16432,19 +16428,19 @@
         </is>
       </c>
       <c r="E69" s="24" t="n">
-        <v>27.1298</v>
+        <v>27.1297</v>
       </c>
       <c r="F69" s="24" t="n">
-        <v>40.6947</v>
+        <v>40.6946</v>
       </c>
       <c r="G69" s="24" t="n">
-        <v>62.3986</v>
+        <v>62.3983</v>
       </c>
       <c r="H69" s="24" t="n">
-        <v>81.3895</v>
+        <v>81.3891</v>
       </c>
       <c r="I69" s="24" t="n">
-        <v>81.3895</v>
+        <v>81.3891</v>
       </c>
       <c r="J69" s="26" t="inlineStr">
         <is>
@@ -16452,10 +16448,10 @@
         </is>
       </c>
       <c r="K69" s="24" t="n">
-        <v>6.8012</v>
+        <v>7.2525</v>
       </c>
       <c r="L69" s="24" t="n">
-        <v>40.6947</v>
+        <v>40.6946</v>
       </c>
     </row>
     <row r="70">
@@ -16470,7 +16466,7 @@
         </is>
       </c>
       <c r="C70" s="24" t="n">
-        <v>107.11</v>
+        <v>113.75</v>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
@@ -16478,19 +16474,19 @@
         </is>
       </c>
       <c r="E70" s="24" t="n">
-        <v>5.9158</v>
+        <v>4.4156</v>
       </c>
       <c r="F70" s="24" t="n">
-        <v>8.873699999999999</v>
+        <v>6.6234</v>
       </c>
       <c r="G70" s="24" t="n">
-        <v>13.6063</v>
+        <v>10.1559</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>17.7473</v>
+        <v>13.2469</v>
       </c>
       <c r="I70" s="24" t="n">
-        <v>17.7473</v>
+        <v>13.2469</v>
       </c>
       <c r="J70" s="26" t="inlineStr">
         <is>
@@ -16498,10 +16494,10 @@
         </is>
       </c>
       <c r="K70" s="24" t="n">
-        <v>9.052899999999999</v>
+        <v>12.8804</v>
       </c>
       <c r="L70" s="24" t="n">
-        <v>8.873699999999999</v>
+        <v>6.6234</v>
       </c>
     </row>
   </sheetData>
@@ -21457,7 +21453,7 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>343.045</v>
+        <v>345.79</v>
       </c>
       <c r="D52" s="32" t="n">
         <v>152198000000</v>
@@ -21543,7 +21539,7 @@
         </is>
       </c>
       <c r="C53" s="34" t="n">
-        <v>253.56</v>
+        <v>260.5</v>
       </c>
       <c r="D53" s="32" t="n">
         <v>90623000000</v>
@@ -21631,7 +21627,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>503.515</v>
+        <v>521.963</v>
       </c>
       <c r="D54" s="32" t="inlineStr"/>
       <c r="E54" s="32" t="n">
@@ -21703,7 +21699,7 @@
         </is>
       </c>
       <c r="C55" s="34" t="n">
-        <v>283.66</v>
+        <v>338.28</v>
       </c>
       <c r="D55" s="32" t="n">
         <v>1749124000</v>
@@ -21789,7 +21785,7 @@
         </is>
       </c>
       <c r="C56" s="34" t="n">
-        <v>167.445</v>
+        <v>191.55</v>
       </c>
       <c r="D56" s="32" t="n">
         <v>2322900000</v>
@@ -21875,7 +21871,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>358.794</v>
+        <v>355.5</v>
       </c>
       <c r="D57" s="32" t="n">
         <v>137196000000</v>
@@ -21963,7 +21959,7 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>269.136</v>
+        <v>249.5</v>
       </c>
       <c r="D58" s="32" t="n">
         <v>31538000000</v>
@@ -22047,7 +22043,7 @@
         </is>
       </c>
       <c r="C59" s="34" t="n">
-        <v>87.78</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="D59" s="32" t="n">
         <v>13046000000</v>
@@ -22135,7 +22131,7 @@
         </is>
       </c>
       <c r="C60" s="34" t="n">
-        <v>1146.22</v>
+        <v>1174.33</v>
       </c>
       <c r="D60" s="32" t="n">
         <v>26708000000</v>
@@ -22163,7 +22159,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="32" t="n">
-        <v>0.7375119999999999</v>
+        <v>0.686949</v>
       </c>
       <c r="P60" s="32" t="n">
         <v>10.32</v>
@@ -22221,7 +22217,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>495.83</v>
+        <v>546.715</v>
       </c>
       <c r="D61" s="32" t="n">
         <v>90007000000</v>
@@ -22307,7 +22303,7 @@
         </is>
       </c>
       <c r="C62" s="34" t="n">
-        <v>147.92</v>
+        <v>153.786</v>
       </c>
       <c r="D62" s="32" t="n">
         <v>130869000</v>
@@ -22393,7 +22389,7 @@
         </is>
       </c>
       <c r="C63" s="34" t="n">
-        <v>219.54</v>
+        <v>224.73</v>
       </c>
       <c r="D63" s="32" t="n">
         <v>160482000000</v>
@@ -22481,7 +22477,7 @@
         </is>
       </c>
       <c r="C64" s="34" t="n">
-        <v>146.33</v>
+        <v>152.815</v>
       </c>
       <c r="D64" s="32" t="n">
         <v>21203000000</v>
@@ -22567,7 +22563,7 @@
         </is>
       </c>
       <c r="C65" s="34" t="n">
-        <v>32.975</v>
+        <v>32.115</v>
       </c>
       <c r="D65" s="32" t="n">
         <v>991962000</v>
@@ -22655,7 +22651,7 @@
         </is>
       </c>
       <c r="C66" s="34" t="n">
-        <v>365.1</v>
+        <v>376</v>
       </c>
       <c r="D66" s="32" t="n">
         <v>30641000000</v>
@@ -22713,7 +22709,7 @@
         <v>18.31</v>
       </c>
       <c r="Y66" s="32" t="n">
-        <v>35.27</v>
+        <v>19.93</v>
       </c>
       <c r="Z66" s="32" t="n">
         <v>-1.47</v>
@@ -22743,7 +22739,7 @@
         </is>
       </c>
       <c r="C67" s="34" t="n">
-        <v>431.57</v>
+        <v>441.82</v>
       </c>
       <c r="D67" s="32" t="n">
         <v>1382678381000</v>
@@ -22831,7 +22827,7 @@
         </is>
       </c>
       <c r="C68" s="34" t="n">
-        <v>373.955</v>
+        <v>378.04</v>
       </c>
       <c r="D68" s="32" t="n">
         <v>113631000000</v>
@@ -22917,7 +22913,7 @@
         </is>
       </c>
       <c r="C69" s="34" t="n">
-        <v>369.03</v>
+        <v>393.515</v>
       </c>
       <c r="D69" s="32" t="n">
         <v>12362000000</v>
@@ -23003,7 +22999,7 @@
         </is>
       </c>
       <c r="C70" s="34" t="n">
-        <v>107.11</v>
+        <v>113.75</v>
       </c>
       <c r="D70" s="32" t="n">
         <v>201191000000</v>
@@ -26236,7 +26232,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>343.045</v>
+        <v>345.79</v>
       </c>
       <c r="D52" s="22" t="n">
         <v>3</v>
@@ -26297,7 +26293,7 @@
         </is>
       </c>
       <c r="C53" s="24" t="n">
-        <v>253.56</v>
+        <v>260.5</v>
       </c>
       <c r="D53" s="22" t="n">
         <v>2.5</v>
@@ -26358,7 +26354,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>503.515</v>
+        <v>521.963</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>5</v>
@@ -26419,7 +26415,7 @@
         </is>
       </c>
       <c r="C55" s="24" t="n">
-        <v>283.66</v>
+        <v>338.28</v>
       </c>
       <c r="D55" s="22" t="n">
         <v>2</v>
@@ -26480,7 +26476,7 @@
         </is>
       </c>
       <c r="C56" s="24" t="n">
-        <v>167.445</v>
+        <v>191.55</v>
       </c>
       <c r="D56" s="22" t="n">
         <v>2</v>
@@ -26541,7 +26537,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>358.794</v>
+        <v>355.5</v>
       </c>
       <c r="D57" s="22" t="n">
         <v>2.5</v>
@@ -26602,7 +26598,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>269.136</v>
+        <v>249.5</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>3</v>
@@ -26663,7 +26659,7 @@
         </is>
       </c>
       <c r="C59" s="24" t="n">
-        <v>87.78</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="D59" s="22" t="n">
         <v>1.5</v>
@@ -26724,7 +26720,7 @@
         </is>
       </c>
       <c r="C60" s="24" t="n">
-        <v>1146.22</v>
+        <v>1174.33</v>
       </c>
       <c r="D60" s="22" t="n">
         <v>2.5</v>
@@ -26785,7 +26781,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>495.83</v>
+        <v>546.715</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>2.5</v>
@@ -26846,7 +26842,7 @@
         </is>
       </c>
       <c r="C62" s="29" t="n">
-        <v>147.92</v>
+        <v>153.786</v>
       </c>
       <c r="D62" s="27" t="n">
         <v>2</v>
@@ -26907,7 +26903,7 @@
         </is>
       </c>
       <c r="C63" s="24" t="n">
-        <v>219.54</v>
+        <v>224.73</v>
       </c>
       <c r="D63" s="22" t="n">
         <v>3</v>
@@ -26968,7 +26964,7 @@
         </is>
       </c>
       <c r="C64" s="24" t="n">
-        <v>146.33</v>
+        <v>152.815</v>
       </c>
       <c r="D64" s="22" t="n">
         <v>2</v>
@@ -27029,7 +27025,7 @@
         </is>
       </c>
       <c r="C65" s="24" t="n">
-        <v>32.975</v>
+        <v>32.115</v>
       </c>
       <c r="D65" s="22" t="n">
         <v>2</v>
@@ -27090,7 +27086,7 @@
         </is>
       </c>
       <c r="C66" s="24" t="n">
-        <v>365.1</v>
+        <v>376</v>
       </c>
       <c r="D66" s="22" t="n">
         <v>1.3</v>
@@ -27151,7 +27147,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>431.57</v>
+        <v>441.82</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>7.2</v>
@@ -27172,7 +27168,7 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
@@ -27212,7 +27208,7 @@
         </is>
       </c>
       <c r="C68" s="14" t="n">
-        <v>373.955</v>
+        <v>378.04</v>
       </c>
       <c r="D68" s="12" t="n">
         <v>2.5</v>
@@ -27273,7 +27269,7 @@
         </is>
       </c>
       <c r="C69" s="24" t="n">
-        <v>369.03</v>
+        <v>393.515</v>
       </c>
       <c r="D69" s="22" t="n">
         <v>2.5</v>
@@ -27334,7 +27330,7 @@
         </is>
       </c>
       <c r="C70" s="24" t="n">
-        <v>107.11</v>
+        <v>113.75</v>
       </c>
       <c r="D70" s="22" t="n">
         <v>2</v>
@@ -27355,7 +27351,7 @@
         </is>
       </c>
       <c r="H70" s="22" t="n">
-        <v>66.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I70" s="23" t="inlineStr">
         <is>
